--- a/consulting_forms/038_executive_insight_consulting_contact_form--consulting_forms.xlsx
+++ b/consulting_forms/038_executive_insight_consulting_contact_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
